--- a/project-management/schedule/Project_Schedule_Gantt_SmartParking.xlsx
+++ b/project-management/schedule/Project_Schedule_Gantt_SmartParking.xlsx
@@ -148,99 +148,102 @@
     <t>3.3, 4.3</t>
   </si>
   <si>
+    <t>Configuración del comportamiento de sensores</t>
+  </si>
+  <si>
+    <t>Control de LEDs</t>
+  </si>
+  <si>
+    <t>Santiago y Fernando</t>
+  </si>
+  <si>
+    <t>Diseño de interfaz de usuario</t>
+  </si>
+  <si>
+    <t>Navegación y priorización de funcionalidades</t>
+  </si>
+  <si>
+    <t>Registro e inicio de sesión</t>
+  </si>
+  <si>
+    <t>4.3, 6.2</t>
+  </si>
+  <si>
+    <t>Flujo de reservas</t>
+  </si>
+  <si>
+    <t>Flujo general de navegación y trazabilidad</t>
+  </si>
+  <si>
+    <t>Conexión de endpoints</t>
+  </si>
+  <si>
+    <t>Conexión API–Supabase</t>
+  </si>
+  <si>
+    <t>8.1, 4.3</t>
+  </si>
+  <si>
+    <t>Desarrollo de lógica de negocio</t>
+  </si>
+  <si>
+    <t>8.2, 7.2</t>
+  </si>
+  <si>
+    <t>Configuración del broker MQTT</t>
+  </si>
+  <si>
+    <t>Fernando y Santiago</t>
+  </si>
+  <si>
+    <t>Formato y estándares de comunicación</t>
+  </si>
+  <si>
+    <t>Pruebas de conexión MQTT</t>
+  </si>
+  <si>
+    <t>9.2, 5.1</t>
+  </si>
+  <si>
+    <t>En progreso</t>
+  </si>
+  <si>
+    <t>Configuración de Stripe y flujo de pago</t>
+  </si>
+  <si>
+    <t>8.3, 7.2</t>
+  </si>
+  <si>
+    <t>Pruebas de transacciones</t>
+  </si>
+  <si>
+    <t>Configuración de Firebase Cloud Messaging</t>
+  </si>
+  <si>
+    <t>Envío de notificaciones push</t>
+  </si>
+  <si>
+    <t>Cálculo del porcentaje de comisión</t>
+  </si>
+  <si>
+    <t>Integración de comisión en backend</t>
+  </si>
+  <si>
+    <t>Equipo estudiantil</t>
+  </si>
+  <si>
+    <t>12.1, 8.3</t>
+  </si>
+  <si>
+    <t>Recordatorios de reserva activa</t>
+  </si>
+  <si>
+    <t>11.2, 7.2</t>
+  </si>
+  <si>
     <t>No iniciada</t>
   </si>
   <si>
-    <t>Configuración del comportamiento de sensores</t>
-  </si>
-  <si>
-    <t>Control de LEDs</t>
-  </si>
-  <si>
-    <t>Santiago y Fernando</t>
-  </si>
-  <si>
-    <t>Diseño de interfaz de usuario</t>
-  </si>
-  <si>
-    <t>Navegación y priorización de funcionalidades</t>
-  </si>
-  <si>
-    <t>Registro e inicio de sesión</t>
-  </si>
-  <si>
-    <t>4.3, 6.2</t>
-  </si>
-  <si>
-    <t>Flujo de reservas</t>
-  </si>
-  <si>
-    <t>Flujo general de navegación y trazabilidad</t>
-  </si>
-  <si>
-    <t>Conexión de endpoints</t>
-  </si>
-  <si>
-    <t>Conexión API–Supabase</t>
-  </si>
-  <si>
-    <t>8.1, 4.3</t>
-  </si>
-  <si>
-    <t>Desarrollo de lógica de negocio</t>
-  </si>
-  <si>
-    <t>8.2, 7.2</t>
-  </si>
-  <si>
-    <t>Configuración del broker MQTT</t>
-  </si>
-  <si>
-    <t>Fernando y Santiago</t>
-  </si>
-  <si>
-    <t>Formato y estándares de comunicación</t>
-  </si>
-  <si>
-    <t>Pruebas de conexión MQTT</t>
-  </si>
-  <si>
-    <t>9.2, 5.1</t>
-  </si>
-  <si>
-    <t>Configuración de Stripe y flujo de pago</t>
-  </si>
-  <si>
-    <t>8.3, 7.2</t>
-  </si>
-  <si>
-    <t>Pruebas de transacciones</t>
-  </si>
-  <si>
-    <t>Configuración de Firebase Cloud Messaging</t>
-  </si>
-  <si>
-    <t>Envío de notificaciones push</t>
-  </si>
-  <si>
-    <t>Cálculo del porcentaje de comisión</t>
-  </si>
-  <si>
-    <t>Integración de comisión en backend</t>
-  </si>
-  <si>
-    <t>Equipo estudiantil</t>
-  </si>
-  <si>
-    <t>12.1, 8.3</t>
-  </si>
-  <si>
-    <t>Recordatorios de reserva activa</t>
-  </si>
-  <si>
-    <t>11.2, 7.2</t>
-  </si>
-  <si>
     <t>Vista detallada de la reserva</t>
   </si>
   <si>
@@ -344,9 +347,6 @@
   </si>
   <si>
     <t>Todas las actividades</t>
-  </si>
-  <si>
-    <t>En progreso</t>
   </si>
 </sst>
 </file>
@@ -1657,7 +1657,7 @@
         <v>19</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="K17" s="27"/>
       <c r="L17" s="25"/>
@@ -1681,7 +1681,7 @@
         <v>46058.0</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>26</v>
@@ -1702,8 +1702,8 @@
       <c r="H18" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I18" s="20" t="s">
-        <v>45</v>
+      <c r="I18" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="K18" s="27"/>
       <c r="L18" s="25"/>
@@ -1727,10 +1727,10 @@
         <v>46086.0</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>47</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>48</v>
       </c>
       <c r="D19" s="11">
         <v>46293.0</v>
@@ -1748,8 +1748,8 @@
       <c r="H19" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I19" s="20" t="s">
-        <v>45</v>
+      <c r="I19" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="K19" s="27"/>
       <c r="L19" s="25"/>
@@ -1773,7 +1773,7 @@
         <v>46028.0</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C20" s="10" t="s">
         <v>17</v>
@@ -1794,8 +1794,8 @@
       <c r="H20" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I20" s="20" t="s">
-        <v>45</v>
+      <c r="I20" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="K20" s="27"/>
       <c r="L20" s="25"/>
@@ -1819,7 +1819,7 @@
         <v>46059.0</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C21" s="10" t="s">
         <v>17</v>
@@ -1840,8 +1840,8 @@
       <c r="H21" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I21" s="20" t="s">
-        <v>45</v>
+      <c r="I21" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="K21" s="27"/>
       <c r="L21" s="25"/>
@@ -1865,7 +1865,7 @@
         <v>46029.0</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>28</v>
@@ -1881,13 +1881,13 @@
         <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H22" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I22" s="20" t="s">
-        <v>45</v>
+      <c r="I22" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="K22" s="27"/>
       <c r="L22" s="25"/>
@@ -1911,7 +1911,7 @@
         <v>46060.0</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>39</v>
@@ -1932,8 +1932,8 @@
       <c r="H23" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I23" s="20" t="s">
-        <v>45</v>
+      <c r="I23" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="K23" s="27"/>
       <c r="L23" s="25"/>
@@ -1957,7 +1957,7 @@
         <v>46088.0</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>17</v>
@@ -1978,8 +1978,8 @@
       <c r="H24" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I24" s="20" t="s">
-        <v>45</v>
+      <c r="I24" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="K24" s="27"/>
       <c r="L24" s="25"/>
@@ -2003,7 +2003,7 @@
         <v>46030.0</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>17</v>
@@ -2024,8 +2024,8 @@
       <c r="H25" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I25" s="20" t="s">
-        <v>45</v>
+      <c r="I25" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="K25" s="27"/>
       <c r="L25" s="25"/>
@@ -2049,7 +2049,7 @@
         <v>46061.0</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C26" s="10" t="s">
         <v>17</v>
@@ -2065,13 +2065,13 @@
         <v>3</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H26" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I26" s="20" t="s">
-        <v>45</v>
+      <c r="I26" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="K26" s="27"/>
       <c r="L26" s="25"/>
@@ -2095,7 +2095,7 @@
         <v>46089.0</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>17</v>
@@ -2111,13 +2111,13 @@
         <v>5</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H27" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I27" s="20" t="s">
-        <v>45</v>
+      <c r="I27" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="K27" s="27"/>
       <c r="L27" s="25"/>
@@ -2141,10 +2141,10 @@
         <v>46031.0</v>
       </c>
       <c r="B28" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>60</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>61</v>
       </c>
       <c r="D28" s="11">
         <v>46293.0</v>
@@ -2162,8 +2162,8 @@
       <c r="H28" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I28" s="20" t="s">
-        <v>45</v>
+      <c r="I28" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="K28" s="27"/>
       <c r="L28" s="25"/>
@@ -2187,10 +2187,10 @@
         <v>46062.0</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D29" s="11">
         <v>46296.0</v>
@@ -2208,8 +2208,8 @@
       <c r="H29" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I29" s="20" t="s">
-        <v>45</v>
+      <c r="I29" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="K29" s="27"/>
       <c r="L29" s="25"/>
@@ -2233,7 +2233,7 @@
         <v>46090.0</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>17</v>
@@ -2249,13 +2249,13 @@
         <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H30" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I30" s="20" t="s">
-        <v>45</v>
+      <c r="I30" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="K30" s="27"/>
       <c r="L30" s="25"/>
@@ -2300,8 +2300,8 @@
       <c r="H31" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I31" s="20" t="s">
-        <v>45</v>
+      <c r="I31" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="K31" s="27"/>
       <c r="L31" s="25"/>
@@ -2346,8 +2346,8 @@
       <c r="H32" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I32" s="20" t="s">
-        <v>45</v>
+      <c r="I32" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="K32" s="27"/>
       <c r="L32" s="25"/>
@@ -2374,7 +2374,7 @@
         <v>68</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D33" s="29">
         <v>46307.0</v>
@@ -2392,8 +2392,8 @@
       <c r="H33" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I33" s="20" t="s">
-        <v>45</v>
+      <c r="I33" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="K33" s="27"/>
       <c r="L33" s="25"/>
@@ -2438,8 +2438,8 @@
       <c r="H34" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I34" s="20" t="s">
-        <v>45</v>
+      <c r="I34" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="K34" s="27"/>
       <c r="L34" s="25"/>
@@ -2484,8 +2484,8 @@
       <c r="H35" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="I35" s="20" t="s">
-        <v>45</v>
+      <c r="I35" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="K35" s="27"/>
       <c r="L35" s="25"/>
@@ -2530,8 +2530,8 @@
       <c r="H36" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="I36" s="20" t="s">
-        <v>45</v>
+      <c r="I36" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="K36" s="27"/>
       <c r="L36" s="25"/>
@@ -2577,7 +2577,7 @@
         <v>19</v>
       </c>
       <c r="I37" s="20" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K37" s="27"/>
       <c r="L37" s="25"/>
@@ -2601,7 +2601,7 @@
         <v>46066.0</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>39</v>
@@ -2617,13 +2617,13 @@
         <v>2</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H38" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I38" s="20" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K38" s="27"/>
       <c r="L38" s="25"/>
@@ -2647,7 +2647,7 @@
         <v>46036.0</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C39" s="10" t="s">
         <v>28</v>
@@ -2669,7 +2669,7 @@
         <v>19</v>
       </c>
       <c r="I39" s="20" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K39" s="27"/>
       <c r="L39" s="25"/>
@@ -2693,7 +2693,7 @@
         <v>46067.0</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>42</v>
@@ -2715,7 +2715,7 @@
         <v>30</v>
       </c>
       <c r="I40" s="20" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K40" s="27"/>
       <c r="L40" s="25"/>
@@ -2739,7 +2739,7 @@
         <v>46037.0</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C41" s="10" t="s">
         <v>26</v>
@@ -2755,13 +2755,13 @@
         <v>3</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H41" s="20" t="s">
         <v>19</v>
       </c>
       <c r="I41" s="20" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K41" s="27"/>
       <c r="L41" s="25"/>
@@ -2785,7 +2785,7 @@
         <v>46068.0</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C42" s="10" t="s">
         <v>72</v>
@@ -2801,13 +2801,13 @@
         <v>5</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H42" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I42" s="20" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K42" s="27"/>
       <c r="L42" s="25"/>
@@ -2831,7 +2831,7 @@
         <v>46038.0</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>26</v>
@@ -2853,7 +2853,7 @@
         <v>19</v>
       </c>
       <c r="I43" s="20" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K43" s="27"/>
       <c r="L43" s="25"/>
@@ -2877,7 +2877,7 @@
         <v>46069.0</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C44" s="10" t="s">
         <v>26</v>
@@ -2899,7 +2899,7 @@
         <v>30</v>
       </c>
       <c r="I44" s="20" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K44" s="27"/>
       <c r="L44" s="25"/>
@@ -2923,10 +2923,10 @@
         <v>46039.0</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D45" s="11">
         <v>46342.0</v>
@@ -2939,13 +2939,13 @@
         <v>3</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H45" s="20" t="s">
         <v>19</v>
       </c>
       <c r="I45" s="20" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K45" s="27"/>
       <c r="L45" s="25"/>
@@ -2969,7 +2969,7 @@
         <v>46070.0</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>17</v>
@@ -2991,7 +2991,7 @@
         <v>30</v>
       </c>
       <c r="I46" s="14" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K46" s="27"/>
       <c r="L46" s="25"/>
@@ -3015,7 +3015,7 @@
         <v>46040.0</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>17</v>
@@ -3031,13 +3031,13 @@
         <v>3</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H47" s="14" t="s">
         <v>19</v>
       </c>
       <c r="I47" s="14" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K47" s="27"/>
       <c r="L47" s="25"/>
@@ -3061,7 +3061,7 @@
         <v>46071.0</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>17</v>
@@ -3077,13 +3077,13 @@
         <v>4</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H48" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I48" s="14" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K48" s="27"/>
       <c r="L48" s="25"/>
@@ -3107,7 +3107,7 @@
         <v>46041.0</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>17</v>
@@ -3123,13 +3123,13 @@
         <v>30</v>
       </c>
       <c r="G49" s="30" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H49" s="14" t="s">
         <v>19</v>
       </c>
       <c r="I49" s="14" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K49" s="27"/>
       <c r="L49" s="25"/>
@@ -3153,7 +3153,7 @@
         <v>46042.0</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>17</v>
@@ -3175,7 +3175,7 @@
         <v>19</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K50" s="27"/>
       <c r="L50" s="25"/>
@@ -3199,7 +3199,7 @@
         <v>46073.0</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>17</v>
@@ -3215,13 +3215,13 @@
         <v>2</v>
       </c>
       <c r="G51" s="30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H51" s="14" t="s">
         <v>30</v>
       </c>
       <c r="I51" s="14" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
       <c r="K51" s="32"/>
       <c r="L51" s="33"/>
@@ -3641,28 +3641,28 @@
         <v>2</v>
       </c>
       <c r="B158" s="37" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C158" s="37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D158" s="37" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E158" s="37" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F158" s="38" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G158" s="37" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H158" s="37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I158" s="37" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="159" ht="15.75" customHeight="1">
@@ -3688,7 +3688,7 @@
         <v>18</v>
       </c>
       <c r="H159" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I159" s="40" t="s">
         <v>20</v>
@@ -3717,7 +3717,7 @@
         <v>46023.0</v>
       </c>
       <c r="H160" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I160" s="40" t="s">
         <v>20</v>
@@ -3746,7 +3746,7 @@
         <v>29</v>
       </c>
       <c r="H161" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I161" s="40" t="s">
         <v>20</v>
@@ -3775,7 +3775,7 @@
         <v>46023.0</v>
       </c>
       <c r="H162" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I162" s="40" t="s">
         <v>20</v>
@@ -3804,7 +3804,7 @@
         <v>46024.0</v>
       </c>
       <c r="H163" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I163" s="40" t="s">
         <v>20</v>
@@ -3833,7 +3833,7 @@
         <v>46055.0</v>
       </c>
       <c r="H164" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I164" s="40" t="s">
         <v>20</v>
@@ -3862,10 +3862,10 @@
         <v>46082.0</v>
       </c>
       <c r="H165" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I165" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="166" ht="15.75" customHeight="1">
@@ -3891,10 +3891,10 @@
         <v>46025.0</v>
       </c>
       <c r="H166" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I166" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="167" ht="15.75" customHeight="1">
@@ -3920,10 +3920,10 @@
         <v>37</v>
       </c>
       <c r="H167" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I167" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="168" ht="15.75" customHeight="1">
@@ -3949,10 +3949,10 @@
         <v>46082.0</v>
       </c>
       <c r="H168" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I168" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="169" ht="15.75" customHeight="1">
@@ -3978,10 +3978,10 @@
         <v>46026.0</v>
       </c>
       <c r="H169" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I169" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="170" ht="15.75" customHeight="1">
@@ -4007,10 +4007,10 @@
         <v>46057.0</v>
       </c>
       <c r="H170" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I170" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="171" ht="15.75" customHeight="1">
@@ -4036,10 +4036,10 @@
         <v>44</v>
       </c>
       <c r="H171" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I171" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="172" ht="15.75" customHeight="1">
@@ -4047,7 +4047,7 @@
         <v>46058.0</v>
       </c>
       <c r="B172" s="40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C172" s="40" t="s">
         <v>26</v>
@@ -4065,10 +4065,10 @@
         <v>46027.0</v>
       </c>
       <c r="H172" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I172" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="173" ht="15.75" customHeight="1">
@@ -4076,10 +4076,10 @@
         <v>46086.0</v>
       </c>
       <c r="B173" s="40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C173" s="40" t="s">
         <v>47</v>
-      </c>
-      <c r="C173" s="40" t="s">
-        <v>48</v>
       </c>
       <c r="D173" s="41">
         <v>46287.0</v>
@@ -4094,10 +4094,10 @@
         <v>46058.0</v>
       </c>
       <c r="H173" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I173" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="174" ht="15.75" customHeight="1">
@@ -4105,7 +4105,7 @@
         <v>46028.0</v>
       </c>
       <c r="B174" s="40" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C174" s="40" t="s">
         <v>17</v>
@@ -4123,10 +4123,10 @@
         <v>46082.0</v>
       </c>
       <c r="H174" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I174" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="175" ht="15.75" customHeight="1">
@@ -4134,7 +4134,7 @@
         <v>46059.0</v>
       </c>
       <c r="B175" s="40" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C175" s="40" t="s">
         <v>17</v>
@@ -4152,10 +4152,10 @@
         <v>46028.0</v>
       </c>
       <c r="H175" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I175" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="176" ht="15.75" customHeight="1">
@@ -4163,7 +4163,7 @@
         <v>46029.0</v>
       </c>
       <c r="B176" s="40" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C176" s="40" t="s">
         <v>28</v>
@@ -4178,13 +4178,13 @@
         <v>2.0</v>
       </c>
       <c r="G176" s="40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H176" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I176" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="177" ht="15.75" customHeight="1">
@@ -4192,7 +4192,7 @@
         <v>46060.0</v>
       </c>
       <c r="B177" s="40" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C177" s="40" t="s">
         <v>39</v>
@@ -4210,10 +4210,10 @@
         <v>46029.0</v>
       </c>
       <c r="H177" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I177" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="178" ht="15.75" customHeight="1">
@@ -4221,7 +4221,7 @@
         <v>46088.0</v>
       </c>
       <c r="B178" s="40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C178" s="40" t="s">
         <v>17</v>
@@ -4239,10 +4239,10 @@
         <v>46060.0</v>
       </c>
       <c r="H178" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I178" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="179" ht="15.75" customHeight="1">
@@ -4250,7 +4250,7 @@
         <v>46030.0</v>
       </c>
       <c r="B179" s="40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C179" s="40" t="s">
         <v>17</v>
@@ -4268,10 +4268,10 @@
         <v>44</v>
       </c>
       <c r="H179" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I179" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="180" ht="15.75" customHeight="1">
@@ -4279,7 +4279,7 @@
         <v>46061.0</v>
       </c>
       <c r="B180" s="40" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C180" s="40" t="s">
         <v>17</v>
@@ -4294,13 +4294,13 @@
         <v>3.0</v>
       </c>
       <c r="G180" s="40" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H180" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I180" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="181" ht="15.75" customHeight="1">
@@ -4308,7 +4308,7 @@
         <v>46089.0</v>
       </c>
       <c r="B181" s="40" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C181" s="40" t="s">
         <v>17</v>
@@ -4323,13 +4323,13 @@
         <v>5.0</v>
       </c>
       <c r="G181" s="40" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H181" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I181" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="182" ht="15.75" customHeight="1">
@@ -4337,10 +4337,10 @@
         <v>46031.0</v>
       </c>
       <c r="B182" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="C182" s="40" t="s">
         <v>60</v>
-      </c>
-      <c r="C182" s="40" t="s">
-        <v>61</v>
       </c>
       <c r="D182" s="41">
         <v>46283.0</v>
@@ -4355,10 +4355,10 @@
         <v>46084.0</v>
       </c>
       <c r="H182" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I182" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="183" ht="15.75" customHeight="1">
@@ -4366,10 +4366,10 @@
         <v>46062.0</v>
       </c>
       <c r="B183" s="40" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C183" s="40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D183" s="41">
         <v>46286.0</v>
@@ -4384,10 +4384,10 @@
         <v>46031.0</v>
       </c>
       <c r="H183" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I183" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="184" ht="15.75" customHeight="1">
@@ -4395,7 +4395,7 @@
         <v>46090.0</v>
       </c>
       <c r="B184" s="40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C184" s="40" t="s">
         <v>17</v>
@@ -4410,13 +4410,13 @@
         <v>1.0</v>
       </c>
       <c r="G184" s="40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H184" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I184" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="185" ht="15.75" customHeight="1">
@@ -4442,10 +4442,10 @@
         <v>66</v>
       </c>
       <c r="H185" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I185" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="186" ht="15.75" customHeight="1">
@@ -4471,10 +4471,10 @@
         <v>46032.0</v>
       </c>
       <c r="H186" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I186" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="187" ht="15.75" customHeight="1">
@@ -4485,7 +4485,7 @@
         <v>68</v>
       </c>
       <c r="C187" s="40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D187" s="41">
         <v>46295.0</v>
@@ -4500,10 +4500,10 @@
         <v>46029.0</v>
       </c>
       <c r="H187" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I187" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="188" ht="15.75" customHeight="1">
@@ -4529,10 +4529,10 @@
         <v>46033.0</v>
       </c>
       <c r="H188" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I188" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="189" ht="15.75" customHeight="1">
@@ -4558,10 +4558,10 @@
         <v>46089.0</v>
       </c>
       <c r="H189" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I189" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="190" ht="15.75" customHeight="1">
@@ -4587,10 +4587,10 @@
         <v>73</v>
       </c>
       <c r="H190" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I190" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="191" ht="15.75" customHeight="1">
@@ -4616,10 +4616,10 @@
         <v>75</v>
       </c>
       <c r="H191" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I191" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="192" ht="15.75" customHeight="1">
@@ -4627,7 +4627,7 @@
         <v>46066.0</v>
       </c>
       <c r="B192" s="40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C192" s="40" t="s">
         <v>39</v>
@@ -4642,13 +4642,13 @@
         <v>2.0</v>
       </c>
       <c r="G192" s="40" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H192" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I192" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="193" ht="15.75" customHeight="1">
@@ -4656,7 +4656,7 @@
         <v>46036.0</v>
       </c>
       <c r="B193" s="40" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C193" s="40" t="s">
         <v>28</v>
@@ -4674,10 +4674,10 @@
         <v>46032.0</v>
       </c>
       <c r="H193" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I193" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="194" ht="15.75" customHeight="1">
@@ -4685,7 +4685,7 @@
         <v>46067.0</v>
       </c>
       <c r="B194" s="40" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C194" s="40" t="s">
         <v>42</v>
@@ -4703,10 +4703,10 @@
         <v>46036.0</v>
       </c>
       <c r="H194" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I194" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1">
@@ -4714,7 +4714,7 @@
         <v>46037.0</v>
       </c>
       <c r="B195" s="40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C195" s="40" t="s">
         <v>26</v>
@@ -4729,13 +4729,13 @@
         <v>3.0</v>
       </c>
       <c r="G195" s="40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H195" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I195" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="196" ht="15.75" customHeight="1">
@@ -4743,7 +4743,7 @@
         <v>46068.0</v>
       </c>
       <c r="B196" s="40" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C196" s="40" t="s">
         <v>72</v>
@@ -4758,13 +4758,13 @@
         <v>5.0</v>
       </c>
       <c r="G196" s="40" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H196" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I196" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="197" ht="15.75" customHeight="1">
@@ -4772,7 +4772,7 @@
         <v>46038.0</v>
       </c>
       <c r="B197" s="40" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C197" s="40" t="s">
         <v>26</v>
@@ -4790,10 +4790,10 @@
         <v>46037.0</v>
       </c>
       <c r="H197" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I197" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="198" ht="15.75" customHeight="1">
@@ -4801,7 +4801,7 @@
         <v>46069.0</v>
       </c>
       <c r="B198" s="40" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C198" s="40" t="s">
         <v>26</v>
@@ -4819,10 +4819,10 @@
         <v>46038.0</v>
       </c>
       <c r="H198" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I198" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="199" ht="15.75" customHeight="1">
@@ -4830,10 +4830,10 @@
         <v>46039.0</v>
       </c>
       <c r="B199" s="40" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C199" s="40" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D199" s="41">
         <v>46304.0</v>
@@ -4845,13 +4845,13 @@
         <v>3.0</v>
       </c>
       <c r="G199" s="40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H199" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I199" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="200" ht="15.75" customHeight="1">
@@ -4859,7 +4859,7 @@
         <v>46070.0</v>
       </c>
       <c r="B200" s="40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C200" s="40" t="s">
         <v>17</v>
@@ -4877,10 +4877,10 @@
         <v>46039.0</v>
       </c>
       <c r="H200" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I200" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="201" ht="15.75" customHeight="1">
@@ -4888,7 +4888,7 @@
         <v>46040.0</v>
       </c>
       <c r="B201" s="40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C201" s="40" t="s">
         <v>17</v>
@@ -4903,13 +4903,13 @@
         <v>3.0</v>
       </c>
       <c r="G201" s="40" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H201" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I201" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="202" ht="15.75" customHeight="1">
@@ -4917,7 +4917,7 @@
         <v>46071.0</v>
       </c>
       <c r="B202" s="40" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C202" s="40" t="s">
         <v>17</v>
@@ -4932,13 +4932,13 @@
         <v>4.0</v>
       </c>
       <c r="G202" s="40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H202" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I202" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="203" ht="15.75" customHeight="1">
@@ -4946,7 +4946,7 @@
         <v>46041.0</v>
       </c>
       <c r="B203" s="40" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C203" s="40" t="s">
         <v>17</v>
@@ -4961,13 +4961,13 @@
         <v>74.0</v>
       </c>
       <c r="G203" s="40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H203" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I203" s="40" t="s">
-        <v>111</v>
+        <v>64</v>
       </c>
     </row>
     <row r="204" ht="15.75" customHeight="1">
@@ -4975,7 +4975,7 @@
         <v>46042.0</v>
       </c>
       <c r="B204" s="40" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C204" s="40" t="s">
         <v>17</v>
@@ -4993,10 +4993,10 @@
         <v>46071.0</v>
       </c>
       <c r="H204" s="43" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I204" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="205" ht="15.75" customHeight="1">
@@ -5004,7 +5004,7 @@
         <v>46073.0</v>
       </c>
       <c r="B205" s="40" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C205" s="40" t="s">
         <v>17</v>
@@ -5019,13 +5019,13 @@
         <v>2.0</v>
       </c>
       <c r="G205" s="40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H205" s="43" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I205" s="40" t="s">
-        <v>45</v>
+        <v>76</v>
       </c>
     </row>
     <row r="206" ht="15.75" customHeight="1"/>
@@ -5827,10 +5827,10 @@
   <mergeCells count="6">
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A2:U2"/>
+    <mergeCell ref="L4:O4"/>
     <mergeCell ref="P4:S4"/>
+    <mergeCell ref="T4:X4"/>
     <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="T4:X4"/>
-    <mergeCell ref="L4:O4"/>
   </mergeCells>
   <conditionalFormatting sqref="J5">
     <cfRule type="expression" dxfId="5" priority="1">
